--- a/data/satisfaction_detail/2026/1-8月/酒店餐饮客户.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/酒店餐饮客户.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.779655154119583</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.92</v>
+        <v>9.911569314021964</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.84</v>
+        <v>9.89668152156613</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.970995808796223</v>
       </c>
     </row>
     <row r="4">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.856204573186908</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.941664809804234</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.98</v>
+        <v>9.987499602100907</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.99</v>
+        <v>9.993055334500504</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.77</v>
+        <v>9.716765876173802</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.92</v>
+        <v>9.926713353493554</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.49</v>
+        <v>9.758554830494987</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.92</v>
+        <v>9.934720144304737</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.98</v>
+        <v>9.976448362720403</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.860896599289088</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.967319221178842</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.98</v>
+        <v>9.983332802801209</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.99</v>
+        <v>9.993055334500504</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.99</v>
+        <v>9.986110669001008</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.99</v>
+        <v>9.986110669001008</v>
       </c>
     </row>
     <row r="13">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.65812032468566</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.852306223141811</v>
       </c>
     </row>
     <row r="17">
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.42</v>
+        <v>9.640798981378321</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.955880948591437</v>
       </c>
     </row>
     <row r="18">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.929794684068121</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>10</v>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.975971905612717</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.56</v>
+        <v>9.430163267820836</v>
       </c>
     </row>
     <row r="20">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.81</v>
+        <v>9.809968698604701</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.9</v>
+        <v>9.915928696482572</v>
       </c>
     </row>
     <row r="21">
